--- a/config/excel/CfgRoguePolicy.xlsx
+++ b/config/excel/CfgRoguePolicy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRoguePolicy" sheetId="1" r:id="Rc70dbcf13a544fc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRoguePolicy" sheetId="1" r:id="Rdb3bbe9cf6864a80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="General"/>
+  </x:numFmts>
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -28,8 +31,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -44,6 +53,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE6F1"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -58,7 +82,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -111,6 +135,38 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -335,61 +391,87 @@
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="19.799999237060547" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="13" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="13" t="str">
         <x:v>RefreshEnabled</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="13" t="str">
         <x:v>ExtraChoiceEnabled</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="13" t="str">
         <x:v>MaxRefreshes</x:v>
+      </x:c>
+      <x:c r="E1" s="15" t="str">
+        <x:v>MobClearChance</x:v>
+      </x:c>
+      <x:c r="F1" s="15" t="str">
+        <x:v>BossClearReward</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="10" t="str">
+      <x:c r="A2" s="16" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
+      <x:c r="B2" s="16" t="str">
         <x:v>bool</x:v>
       </x:c>
-      <x:c r="C2" s="10" t="str">
+      <x:c r="C2" s="16" t="str">
         <x:v>bool</x:v>
       </x:c>
-      <x:c r="D2" s="10" t="str">
+      <x:c r="D2" s="16" t="str">
         <x:v>int</x:v>
+      </x:c>
+      <x:c r="E2" s="17" t="str">
+        <x:v>number</x:v>
+      </x:c>
+      <x:c r="F2" s="17" t="str">
+        <x:v>bool</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="18" t="str">
         <x:v># 策略编号</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="18" t="str">
         <x:v>刷新功能默认开关</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="18" t="str">
         <x:v>第四项授权默认开关</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="18" t="str">
         <x:v>单次选择最多刷新次数</x:v>
+      </x:c>
+      <x:c r="E3" s="19" t="str">
+        <x:v>小怪房首次清房触发三选一概率</x:v>
+      </x:c>
+      <x:c r="F3" s="19" t="str">
+        <x:v>Boss房首次清房必发三选一</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="6" t="n">
+      <x:c r="A4" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="b">
+      <x:c r="B4" s="21" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="b">
+      <x:c r="C4" s="21" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="6" t="n">
+      <x:c r="D4" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="22" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/config/excel/CfgRoguePolicy.xlsx
+++ b/config/excel/CfgRoguePolicy.xlsx
@@ -393,6 +393,10 @@
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -414,6 +418,18 @@
       <x:c r="F1" s="15" t="str">
         <x:v>BossClearReward</x:v>
       </x:c>
+      <x:c r="G1" s="15" t="str">
+        <x:v>FirstMobClearReward</x:v>
+      </x:c>
+      <x:c r="H1" s="15" t="str">
+        <x:v>MaxConsecutiveMobMisses</x:v>
+      </x:c>
+      <x:c r="I1" s="15" t="str">
+        <x:v>SelectedUpgradeWeightMultiplier</x:v>
+      </x:c>
+      <x:c r="J1" s="15" t="str">
+        <x:v>UnlockedComboWeightMultiplier</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="16" t="str">
@@ -434,6 +450,18 @@
       <x:c r="F2" s="17" t="str">
         <x:v>bool</x:v>
       </x:c>
+      <x:c r="G2" s="17" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="H2" s="17" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="I2" s="17" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="J2" s="17" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
       <x:c r="A3" s="18" t="str">
@@ -454,6 +482,18 @@
       <x:c r="F3" s="19" t="str">
         <x:v>Boss房首次清房必发三选一</x:v>
       </x:c>
+      <x:c r="G3" s="19" t="str">
+        <x:v>首次小怪清房必定给予三选一</x:v>
+      </x:c>
+      <x:c r="H3" s="19" t="str">
+        <x:v>连续未获奖小怪清房上限；0为关闭保底</x:v>
+      </x:c>
+      <x:c r="I3" s="19" t="str">
+        <x:v>已选未满级战斗强化抽取权重倍数</x:v>
+      </x:c>
+      <x:c r="J3" s="19" t="str">
+        <x:v>已满足前置且未选组合强化抽取权重倍数</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
       <x:c r="A4" s="20" t="n">
@@ -473,6 +513,18 @@
       </x:c>
       <x:c r="F4" s="23" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="G4" s="23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I4" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J4" s="20" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/excel/CfgRoguePolicy.xlsx
+++ b/config/excel/CfgRoguePolicy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRoguePolicy" sheetId="1" r:id="Rdb3bbe9cf6864a80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRoguePolicy" sheetId="1" r:id="Ra2b4df9934534817"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -37,8 +37,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -68,6 +73,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDCE6F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAF7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -82,7 +102,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -162,6 +182,21 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -387,145 +422,113 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="19.799999237060547" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="13" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="25" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="25" t="str">
         <x:v>RefreshEnabled</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="25" t="str">
         <x:v>ExtraChoiceEnabled</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
+      <x:c r="D1" s="25" t="str">
         <x:v>MaxRefreshes</x:v>
       </x:c>
-      <x:c r="E1" s="15" t="str">
-        <x:v>MobClearChance</x:v>
-      </x:c>
-      <x:c r="F1" s="15" t="str">
-        <x:v>BossClearReward</x:v>
-      </x:c>
-      <x:c r="G1" s="15" t="str">
-        <x:v>FirstMobClearReward</x:v>
-      </x:c>
-      <x:c r="H1" s="15" t="str">
-        <x:v>MaxConsecutiveMobMisses</x:v>
-      </x:c>
-      <x:c r="I1" s="15" t="str">
+      <x:c r="E1" s="25" t="str">
         <x:v>SelectedUpgradeWeightMultiplier</x:v>
       </x:c>
-      <x:c r="J1" s="15" t="str">
+      <x:c r="F1" s="25" t="str">
         <x:v>UnlockedComboWeightMultiplier</x:v>
       </x:c>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="16" t="str">
+      <x:c r="A2" s="26" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="16" t="str">
+      <x:c r="B2" s="26" t="str">
         <x:v>bool</x:v>
       </x:c>
-      <x:c r="C2" s="16" t="str">
+      <x:c r="C2" s="26" t="str">
         <x:v>bool</x:v>
       </x:c>
-      <x:c r="D2" s="16" t="str">
+      <x:c r="D2" s="26" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E2" s="17" t="str">
-        <x:v>number</x:v>
-      </x:c>
-      <x:c r="F2" s="17" t="str">
-        <x:v>bool</x:v>
-      </x:c>
-      <x:c r="G2" s="17" t="str">
-        <x:v>bool</x:v>
-      </x:c>
-      <x:c r="H2" s="17" t="str">
+      <x:c r="E2" s="26" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="I2" s="17" t="str">
+      <x:c r="F2" s="26" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="J2" s="17" t="str">
-        <x:v>int</x:v>
-      </x:c>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="18" t="str">
+      <x:c r="A3" s="28" t="str">
         <x:v># 策略编号</x:v>
       </x:c>
-      <x:c r="B3" s="18" t="str">
+      <x:c r="B3" s="28" t="str">
         <x:v>刷新功能默认开关</x:v>
       </x:c>
-      <x:c r="C3" s="18" t="str">
+      <x:c r="C3" s="28" t="str">
         <x:v>第四项授权默认开关</x:v>
       </x:c>
-      <x:c r="D3" s="18" t="str">
+      <x:c r="D3" s="28" t="str">
         <x:v>单次选择最多刷新次数</x:v>
       </x:c>
-      <x:c r="E3" s="19" t="str">
-        <x:v>小怪房首次清房触发三选一概率</x:v>
-      </x:c>
-      <x:c r="F3" s="19" t="str">
-        <x:v>Boss房首次清房必发三选一</x:v>
-      </x:c>
-      <x:c r="G3" s="19" t="str">
-        <x:v>首次小怪清房必定给予三选一</x:v>
-      </x:c>
-      <x:c r="H3" s="19" t="str">
-        <x:v>连续未获奖小怪清房上限；0为关闭保底</x:v>
-      </x:c>
-      <x:c r="I3" s="19" t="str">
+      <x:c r="E3" s="28" t="str">
         <x:v>已选未满级战斗强化抽取权重倍数</x:v>
       </x:c>
-      <x:c r="J3" s="19" t="str">
+      <x:c r="F3" s="28" t="str">
         <x:v>已满足前置且未选组合强化抽取权重倍数</x:v>
       </x:c>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
     </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="20" t="n">
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="21" t="b">
+      <x:c r="B4" s="30" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C4" s="21" t="b">
+      <x:c r="C4" s="30" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="20" t="n">
+      <x:c r="D4" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E4" s="22" t="n">
-        <x:v>0.45</x:v>
-      </x:c>
-      <x:c r="F4" s="23" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G4" s="23" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="20" t="n">
+      <x:c r="E4" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F4" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I4" s="20" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J4" s="20" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
